--- a/output/experiment_hall_stats.xlsx
+++ b/output/experiment_hall_stats.xlsx
@@ -498,10 +498,10 @@
         <v>150</v>
       </c>
       <c r="H2" t="n">
-        <v>21.57333333333333</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="I2" t="n">
-        <v>24.61690746891927</v>
+        <v>12.50453251158688</v>
       </c>
     </row>
     <row r="3">
@@ -527,10 +527,10 @@
         <v>400</v>
       </c>
       <c r="H3" t="n">
-        <v>13.115</v>
+        <v>27.36666666666666</v>
       </c>
       <c r="I3" t="n">
-        <v>5.777062402294094</v>
+        <v>11.61091440556399</v>
       </c>
     </row>
     <row r="4">
